--- a/artfynd/A 56185-2025 artfynd.xlsx
+++ b/artfynd/A 56185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031516</v>
+        <v>122031431</v>
       </c>
       <c r="B2" t="n">
-        <v>92086</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699034</v>
+        <v>698850</v>
       </c>
       <c r="R2" t="n">
-        <v>7316711</v>
+        <v>7316749</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031517</v>
+        <v>122031448</v>
       </c>
       <c r="B3" t="n">
-        <v>92086</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698877</v>
+        <v>698757</v>
       </c>
       <c r="R3" t="n">
-        <v>7316482</v>
+        <v>7316498</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031400</v>
+        <v>122031450</v>
       </c>
       <c r="B4" t="n">
-        <v>92279</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698965</v>
+        <v>699129</v>
       </c>
       <c r="R4" t="n">
-        <v>7316856</v>
+        <v>7316858</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1005,6 +990,748 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122031400</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Moskosel, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>698965</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7316856</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122031478</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Moskosel, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>698839</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7316732</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122031516</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Moskosel, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>699034</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7316711</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122031517</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Moskosel, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>698877</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7316482</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122031519</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Moskosel, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>698809</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7316701</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122031508</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Moskosel, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>698899</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7316525</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122031510</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Moskosel, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>699129</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7316858</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56185-2025 artfynd.xlsx
+++ b/artfynd/A 56185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031431</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031448</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031450</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031400</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031478</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031516</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031517</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031519</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031508</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,8 +1782,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031510</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 56185-2025 artfynd.xlsx
+++ b/artfynd/A 56185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,52 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031448</v>
+        <v>135619390</v>
       </c>
       <c r="B3" t="n">
-        <v>90932</v>
+        <v>92220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Moskosel, Pi lm</t>
+          <t>Abmuojarrie, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698757</v>
+        <v>698821</v>
       </c>
       <c r="R3" t="n">
-        <v>7316498</v>
+        <v>7316691</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,24 +886,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031448</t>
+          <t>https://artportalen.se/Sighting/135619390</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031450</v>
+        <v>122031448</v>
       </c>
       <c r="B4" t="n">
         <v>90932</v>
@@ -941,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699129</v>
+        <v>698757</v>
       </c>
       <c r="R4" t="n">
-        <v>7316858</v>
+        <v>7316498</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1007,16 +1008,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031450</t>
+          <t>https://artportalen.se/Sighting/122031448</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031400</v>
+        <v>122031450</v>
       </c>
       <c r="B5" t="n">
-        <v>91962</v>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698965</v>
+        <v>699129</v>
       </c>
       <c r="R5" t="n">
-        <v>7316856</v>
+        <v>7316858</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1118,16 +1119,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031400</t>
+          <t>https://artportalen.se/Sighting/122031450</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031478</v>
+        <v>122031400</v>
       </c>
       <c r="B6" t="n">
-        <v>93197</v>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698839</v>
+        <v>698965</v>
       </c>
       <c r="R6" t="n">
-        <v>7316732</v>
+        <v>7316856</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,58 +1230,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031478</t>
+          <t>https://artportalen.se/Sighting/122031400</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122031516</v>
+        <v>135619375</v>
       </c>
       <c r="B7" t="n">
-        <v>93201</v>
+        <v>92027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Moskosel, Pi lm</t>
+          <t>Abmuojarrie, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699034</v>
+        <v>699075</v>
       </c>
       <c r="R7" t="n">
-        <v>7316711</v>
+        <v>7316688</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,17 +1301,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,49 +1331,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031516</t>
+          <t>https://artportalen.se/Sighting/135619375</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122031517</v>
+        <v>122031478</v>
       </c>
       <c r="B8" t="n">
-        <v>93201</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698877</v>
+        <v>698839</v>
       </c>
       <c r="R8" t="n">
-        <v>7316482</v>
+        <v>7316732</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,13 +1453,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031517</t>
+          <t>https://artportalen.se/Sighting/122031478</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122031519</v>
+        <v>122031516</v>
       </c>
       <c r="B9" t="n">
         <v>93201</v>
@@ -1496,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698809</v>
+        <v>699034</v>
       </c>
       <c r="R9" t="n">
-        <v>7316701</v>
+        <v>7316711</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1562,16 +1564,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031519</t>
+          <t>https://artportalen.se/Sighting/122031516</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122031508</v>
+        <v>122031517</v>
       </c>
       <c r="B10" t="n">
-        <v>93228</v>
+        <v>93201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,21 +1581,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698899</v>
+        <v>698877</v>
       </c>
       <c r="R10" t="n">
-        <v>7316525</v>
+        <v>7316482</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1673,16 +1675,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031508</t>
+          <t>https://artportalen.se/Sighting/122031517</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122031510</v>
+        <v>122031519</v>
       </c>
       <c r="B11" t="n">
-        <v>93228</v>
+        <v>93201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,21 +1692,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699129</v>
+        <v>698809</v>
       </c>
       <c r="R11" t="n">
-        <v>7316858</v>
+        <v>7316701</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1783,6 +1785,2344 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031519</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135619386</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>698897</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7316661</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619386</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135619378</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>699012</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7316709</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619378</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135619384</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>698932</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7316712</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619384</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135619399</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>698983</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7316827</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619399</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135619372</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>699074</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7316957</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619372</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135619373</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>699069</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7316963</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619373</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135619374</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>699143</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7316815</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619374</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135619380</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>699020</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7316718</v>
+      </c>
+      <c r="S19" t="n">
+        <v>19</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619380</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135619385</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>698875</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7316678</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619385</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135619388</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>698804</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7316669</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619388</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135619389</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>698804</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7316670</v>
+      </c>
+      <c r="S22" t="n">
+        <v>36</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619389</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135619397</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>698885</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7316826</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619397</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135619403</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>699002</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7316769</v>
+      </c>
+      <c r="S24" t="n">
+        <v>9</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619403</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135619401</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>699046</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7316872</v>
+      </c>
+      <c r="S25" t="n">
+        <v>29</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619401</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135619402</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>699106</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7316854</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619402</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135619381</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>698995</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7316713</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619381</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135619383</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>698932</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7316712</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619383</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135619387</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>698897</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7316661</v>
+      </c>
+      <c r="S29" t="n">
+        <v>13</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619387</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122031508</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Moskosel, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>698899</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7316525</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031508</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122031510</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Moskosel, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>699129</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7316858</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122031510</t>
         </is>
@@ -1800,6 +4140,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56185-2025 artfynd.xlsx
+++ b/artfynd/A 56185-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135619390</v>
       </c>
       <c r="B3" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135619375</v>
       </c>
       <c r="B7" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>135619386</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135619378</v>
       </c>
       <c r="B13" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>135619384</v>
       </c>
       <c r="B14" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>135619399</v>
       </c>
       <c r="B15" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>135619372</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135619373</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>135619374</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135619380</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135619385</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>135619388</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>135619389</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>135619397</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>135619403</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>135619401</v>
       </c>
       <c r="B25" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>135619402</v>
       </c>
       <c r="B26" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>135619381</v>
       </c>
       <c r="B27" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>135619383</v>
       </c>
       <c r="B28" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135619387</v>
       </c>
       <c r="B29" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56185-2025 artfynd.xlsx
+++ b/artfynd/A 56185-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135619390</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135619375</v>
       </c>
       <c r="B7" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>135619386</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135619378</v>
       </c>
       <c r="B13" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>135619384</v>
       </c>
       <c r="B14" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>135619399</v>
       </c>
       <c r="B15" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>135619381</v>
       </c>
       <c r="B27" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>135619383</v>
       </c>
       <c r="B28" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135619387</v>
       </c>
       <c r="B29" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56185-2025 artfynd.xlsx
+++ b/artfynd/A 56185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,52 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031448</v>
+        <v>135619390</v>
       </c>
       <c r="B3" t="n">
-        <v>90932</v>
+        <v>92294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Moskosel, Pi lm</t>
+          <t>Abmuojarrie, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698757</v>
+        <v>698821</v>
       </c>
       <c r="R3" t="n">
-        <v>7316498</v>
+        <v>7316691</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,24 +886,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031448</t>
+          <t>https://artportalen.se/Sighting/135619390</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031450</v>
+        <v>122031448</v>
       </c>
       <c r="B4" t="n">
         <v>90932</v>
@@ -941,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699129</v>
+        <v>698757</v>
       </c>
       <c r="R4" t="n">
-        <v>7316858</v>
+        <v>7316498</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1007,16 +1008,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031450</t>
+          <t>https://artportalen.se/Sighting/122031448</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031400</v>
+        <v>122031450</v>
       </c>
       <c r="B5" t="n">
-        <v>91962</v>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698965</v>
+        <v>699129</v>
       </c>
       <c r="R5" t="n">
-        <v>7316856</v>
+        <v>7316858</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1118,16 +1119,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031400</t>
+          <t>https://artportalen.se/Sighting/122031450</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031478</v>
+        <v>122031400</v>
       </c>
       <c r="B6" t="n">
-        <v>93197</v>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698839</v>
+        <v>698965</v>
       </c>
       <c r="R6" t="n">
-        <v>7316732</v>
+        <v>7316856</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,58 +1230,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031478</t>
+          <t>https://artportalen.se/Sighting/122031400</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122031516</v>
+        <v>135619375</v>
       </c>
       <c r="B7" t="n">
-        <v>93201</v>
+        <v>92101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Moskosel, Pi lm</t>
+          <t>Abmuojarrie, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699034</v>
+        <v>699075</v>
       </c>
       <c r="R7" t="n">
-        <v>7316711</v>
+        <v>7316688</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,17 +1301,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,49 +1331,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031516</t>
+          <t>https://artportalen.se/Sighting/135619375</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122031517</v>
+        <v>122031478</v>
       </c>
       <c r="B8" t="n">
-        <v>93201</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698877</v>
+        <v>698839</v>
       </c>
       <c r="R8" t="n">
-        <v>7316482</v>
+        <v>7316732</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,13 +1453,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031517</t>
+          <t>https://artportalen.se/Sighting/122031478</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122031519</v>
+        <v>122031516</v>
       </c>
       <c r="B9" t="n">
         <v>93201</v>
@@ -1496,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698809</v>
+        <v>699034</v>
       </c>
       <c r="R9" t="n">
-        <v>7316701</v>
+        <v>7316711</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1562,16 +1564,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031519</t>
+          <t>https://artportalen.se/Sighting/122031516</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122031508</v>
+        <v>122031517</v>
       </c>
       <c r="B10" t="n">
-        <v>93228</v>
+        <v>93201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,21 +1581,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698899</v>
+        <v>698877</v>
       </c>
       <c r="R10" t="n">
-        <v>7316525</v>
+        <v>7316482</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1673,16 +1675,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031508</t>
+          <t>https://artportalen.se/Sighting/122031517</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122031510</v>
+        <v>122031519</v>
       </c>
       <c r="B11" t="n">
-        <v>93228</v>
+        <v>93201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,21 +1692,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699129</v>
+        <v>698809</v>
       </c>
       <c r="R11" t="n">
-        <v>7316858</v>
+        <v>7316701</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1783,6 +1785,2344 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031519</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135619386</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>698897</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7316661</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619386</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135619378</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>699012</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7316709</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619378</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135619384</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>698932</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7316712</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619384</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135619399</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>698983</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7316827</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619399</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135619372</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>699074</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7316957</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619372</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135619373</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>699069</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7316963</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619373</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135619374</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>699143</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7316815</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619374</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135619380</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>699020</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7316718</v>
+      </c>
+      <c r="S19" t="n">
+        <v>19</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619380</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135619385</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>698875</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7316678</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619385</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135619388</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>698804</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7316669</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619388</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135619389</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>698804</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7316670</v>
+      </c>
+      <c r="S22" t="n">
+        <v>36</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619389</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135619397</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>698885</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7316826</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619397</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135619403</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>699002</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7316769</v>
+      </c>
+      <c r="S24" t="n">
+        <v>9</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619403</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135619401</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>699046</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7316872</v>
+      </c>
+      <c r="S25" t="n">
+        <v>29</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619401</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135619402</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>699106</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7316854</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619402</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135619381</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>698995</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7316713</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619381</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135619383</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>698932</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7316712</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619383</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135619387</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Abmuojarrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>698897</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7316661</v>
+      </c>
+      <c r="S29" t="n">
+        <v>13</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619387</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122031508</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Moskosel, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>698899</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7316525</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031508</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122031510</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Moskosel, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>699129</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7316858</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122031510</t>
         </is>
@@ -1800,6 +4140,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56185-2025 artfynd.xlsx
+++ b/artfynd/A 56185-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135619390</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135619375</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56185-2025 artfynd.xlsx
+++ b/artfynd/A 56185-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135619390</v>
       </c>
       <c r="B3" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135619375</v>
       </c>
       <c r="B7" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>135619386</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135619378</v>
       </c>
       <c r="B13" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>135619384</v>
       </c>
       <c r="B14" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>135619399</v>
       </c>
       <c r="B15" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>135619372</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135619373</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>135619374</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135619380</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135619385</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>135619388</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>135619389</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>135619397</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>135619403</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>135619401</v>
       </c>
       <c r="B25" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>135619402</v>
       </c>
       <c r="B26" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>135619381</v>
       </c>
       <c r="B27" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>135619383</v>
       </c>
       <c r="B28" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135619387</v>
       </c>
       <c r="B29" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56185-2025 artfynd.xlsx
+++ b/artfynd/A 56185-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135619390</v>
       </c>
       <c r="B3" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135619375</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>135619386</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135619378</v>
       </c>
       <c r="B13" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>135619384</v>
       </c>
       <c r="B14" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>135619399</v>
       </c>
       <c r="B15" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>135619381</v>
       </c>
       <c r="B27" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>135619383</v>
       </c>
       <c r="B28" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135619387</v>
       </c>
       <c r="B29" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56185-2025 artfynd.xlsx
+++ b/artfynd/A 56185-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135619390</v>
       </c>
       <c r="B3" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135619375</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56185-2025 artfynd.xlsx
+++ b/artfynd/A 56185-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135619390</v>
       </c>
       <c r="B3" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135619375</v>
       </c>
       <c r="B7" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>135619386</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135619378</v>
       </c>
       <c r="B13" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>135619384</v>
       </c>
       <c r="B14" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>135619399</v>
       </c>
       <c r="B15" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>135619372</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135619373</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>135619374</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135619380</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135619385</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>135619388</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>135619389</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>135619397</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>135619403</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>135619401</v>
       </c>
       <c r="B25" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>135619402</v>
       </c>
       <c r="B26" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>135619381</v>
       </c>
       <c r="B27" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>135619383</v>
       </c>
       <c r="B28" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135619387</v>
       </c>
       <c r="B29" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
